--- a/Pruebas_manuales_App.xlsx
+++ b/Pruebas_manuales_App.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\esteticaybellezastrani\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E37AA6EF-F3CF-447D-B7FA-E96CF1659EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D9644F-240E-497A-9355-FA82B21926EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
